--- a/Result/profitability/4523.xlsx
+++ b/Result/profitability/4523.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>2.56125</v>
+        <v>2.52125</v>
       </c>
       <c r="N2" t="n">
-        <v>-29.12375</v>
+        <v>-29.5125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.63</v>
+        <v>2.6275</v>
       </c>
       <c r="N3" t="n">
-        <v>-29.53875</v>
+        <v>-27.3075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2.66125</v>
+        <v>2.8075</v>
       </c>
       <c r="N4" t="n">
-        <v>-27.535</v>
+        <v>-27.555</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>2.83</v>
+        <v>3.21625</v>
       </c>
       <c r="N5" t="n">
-        <v>-29.74375</v>
+        <v>-16.9725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3175</v>
+        <v>-0.47125</v>
       </c>
       <c r="N6" t="n">
-        <v>-16.605</v>
+        <v>16.6125</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.26</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3425</v>
+        <v>-0.25375</v>
       </c>
       <c r="N7" t="n">
-        <v>16.06625</v>
+        <v>20.14</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09875</v>
+        <v>-0.17625</v>
       </c>
       <c r="N8" t="n">
-        <v>19.81625</v>
+        <v>20.52</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.39</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0725</v>
+        <v>0.07250000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>19.78125</v>
@@ -2026,7 +2026,7 @@
         <v>0.74</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="N13" t="n">
         <v>21.42125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4523</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>225</v>
+      </c>
+      <c r="D75" t="n">
+        <v>171</v>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-15.49%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.5175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-28.89875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.133333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.630000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3117386489479514</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8005181347150259</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>102.17</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.301860346585117</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
